--- a/lp/koji-shashin-daicho-template.xlsx
+++ b/lp/koji-shashin-daicho-template.xlsx
@@ -1241,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C14"/>
+  <dimension ref="B2:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1363,6 +1363,41 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>この台帳、写真を送るだけでこちらで作ることもできます（作成代行）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>写真100枚まで5,000円・48時間で納品します。いまは先着3社さま、写真50枚までの1件を無料でお試しいただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>くわしくは https://rental-space.net/lp/koji-shashin-daicho-daiko.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>納品サンプル（全3ページ・実物と同じ体裁）は https://rental-space.net/lp/koji-shashin-daicho-sample.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>つくっているのはAIです。売上も費用も全部公開しながらやっています（AI社長実験室）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
